--- a/project/data/differentiation/**Practical 3 - Model Data - Osteogenesis.xlsx
+++ b/project/data/differentiation/**Practical 3 - Model Data - Osteogenesis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacobpollard/Documents/Uni/Biology/Second year/Sem 2/BABS/babs4_hMSC_proj/project/data/differentiation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD55549-3E07-B248-9FDE-DD5C8618A15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73843DC3-E8CD-034D-8311-5F1ADAD66D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10920" yWindow="660" windowWidth="28800" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Absorbance 1_01" sheetId="1" r:id="rId1"/>
@@ -25,28 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="116">
-  <si>
-    <t>Measurement results</t>
-  </si>
-  <si>
-    <t>BIO00066I Cell Biology pNP March 26 Model plate</t>
-  </si>
-  <si>
-    <t>16/03/2026 12:37:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Absorbance 1</t>
-  </si>
-  <si>
-    <t>Wavelength: 405 nm</t>
-  </si>
-  <si>
-    <t>Plate 1</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Abs</t>
   </si>
@@ -74,306 +53,6 @@
   <si>
     <t>H</t>
   </si>
-  <si>
-    <t>Sample</t>
-  </si>
-  <si>
-    <t>un 0001</t>
-  </si>
-  <si>
-    <t>un 0002</t>
-  </si>
-  <si>
-    <t>un 0003</t>
-  </si>
-  <si>
-    <t>un 0004</t>
-  </si>
-  <si>
-    <t>un 0005</t>
-  </si>
-  <si>
-    <t>un 0006</t>
-  </si>
-  <si>
-    <t>un 0007</t>
-  </si>
-  <si>
-    <t>un 0008</t>
-  </si>
-  <si>
-    <t>un 0009</t>
-  </si>
-  <si>
-    <t>un 0010</t>
-  </si>
-  <si>
-    <t>un 0011</t>
-  </si>
-  <si>
-    <t>un 0012</t>
-  </si>
-  <si>
-    <t>un 0013</t>
-  </si>
-  <si>
-    <t>un 0014</t>
-  </si>
-  <si>
-    <t>un 0015</t>
-  </si>
-  <si>
-    <t>un 0016</t>
-  </si>
-  <si>
-    <t>un 0017</t>
-  </si>
-  <si>
-    <t>un 0018</t>
-  </si>
-  <si>
-    <t>un 0019</t>
-  </si>
-  <si>
-    <t>un 0020</t>
-  </si>
-  <si>
-    <t>un 0021</t>
-  </si>
-  <si>
-    <t>un 0022</t>
-  </si>
-  <si>
-    <t>un 0023</t>
-  </si>
-  <si>
-    <t>un 0024</t>
-  </si>
-  <si>
-    <t>un 0025</t>
-  </si>
-  <si>
-    <t>un 0026</t>
-  </si>
-  <si>
-    <t>un 0027</t>
-  </si>
-  <si>
-    <t>un 0028</t>
-  </si>
-  <si>
-    <t>un 0029</t>
-  </si>
-  <si>
-    <t>un 0030</t>
-  </si>
-  <si>
-    <t>un 0031</t>
-  </si>
-  <si>
-    <t>un 0032</t>
-  </si>
-  <si>
-    <t>un 0033</t>
-  </si>
-  <si>
-    <t>un 0034</t>
-  </si>
-  <si>
-    <t>un 0035</t>
-  </si>
-  <si>
-    <t>un 0036</t>
-  </si>
-  <si>
-    <t>un 0037</t>
-  </si>
-  <si>
-    <t>un 0038</t>
-  </si>
-  <si>
-    <t>un 0039</t>
-  </si>
-  <si>
-    <t>un 0040</t>
-  </si>
-  <si>
-    <t>un 0041</t>
-  </si>
-  <si>
-    <t>un 0042</t>
-  </si>
-  <si>
-    <t>un 0043</t>
-  </si>
-  <si>
-    <t>un 0044</t>
-  </si>
-  <si>
-    <t>un 0045</t>
-  </si>
-  <si>
-    <t>un 0046</t>
-  </si>
-  <si>
-    <t>un 0047</t>
-  </si>
-  <si>
-    <t>un 0048</t>
-  </si>
-  <si>
-    <t>un 0049</t>
-  </si>
-  <si>
-    <t>un 0050</t>
-  </si>
-  <si>
-    <t>un 0051</t>
-  </si>
-  <si>
-    <t>un 0052</t>
-  </si>
-  <si>
-    <t>un 0053</t>
-  </si>
-  <si>
-    <t>un 0054</t>
-  </si>
-  <si>
-    <t>un 0055</t>
-  </si>
-  <si>
-    <t>un 0056</t>
-  </si>
-  <si>
-    <t>un 0057</t>
-  </si>
-  <si>
-    <t>un 0058</t>
-  </si>
-  <si>
-    <t>un 0059</t>
-  </si>
-  <si>
-    <t>un 0060</t>
-  </si>
-  <si>
-    <t>un 0061</t>
-  </si>
-  <si>
-    <t>un 0062</t>
-  </si>
-  <si>
-    <t>un 0063</t>
-  </si>
-  <si>
-    <t>un 0064</t>
-  </si>
-  <si>
-    <t>un 0065</t>
-  </si>
-  <si>
-    <t>un 0066</t>
-  </si>
-  <si>
-    <t>un 0067</t>
-  </si>
-  <si>
-    <t>un 0068</t>
-  </si>
-  <si>
-    <t>un 0069</t>
-  </si>
-  <si>
-    <t>un 0070</t>
-  </si>
-  <si>
-    <t>un 0071</t>
-  </si>
-  <si>
-    <t>un 0072</t>
-  </si>
-  <si>
-    <t>un 0073</t>
-  </si>
-  <si>
-    <t>un 0074</t>
-  </si>
-  <si>
-    <t>un 0075</t>
-  </si>
-  <si>
-    <t>un 0076</t>
-  </si>
-  <si>
-    <t>un 0077</t>
-  </si>
-  <si>
-    <t>un 0078</t>
-  </si>
-  <si>
-    <t>un 0079</t>
-  </si>
-  <si>
-    <t>un 0080</t>
-  </si>
-  <si>
-    <t>un 0081</t>
-  </si>
-  <si>
-    <t>un 0082</t>
-  </si>
-  <si>
-    <t>un 0083</t>
-  </si>
-  <si>
-    <t>un 0084</t>
-  </si>
-  <si>
-    <t>un 0085</t>
-  </si>
-  <si>
-    <t>un 0086</t>
-  </si>
-  <si>
-    <t>un 0087</t>
-  </si>
-  <si>
-    <t>un 0088</t>
-  </si>
-  <si>
-    <t>un 0089</t>
-  </si>
-  <si>
-    <t>un 0090</t>
-  </si>
-  <si>
-    <t>un 0091</t>
-  </si>
-  <si>
-    <t>un 0092</t>
-  </si>
-  <si>
-    <t>un 0093</t>
-  </si>
-  <si>
-    <t>un 0094</t>
-  </si>
-  <si>
-    <t>un 0095</t>
-  </si>
-  <si>
-    <t>un 0096</t>
-  </si>
-  <si>
-    <t>Day 0</t>
-  </si>
-  <si>
-    <t>Day 8</t>
-  </si>
-  <si>
-    <t>Day 8 osteo</t>
-  </si>
 </sst>
 </file>
 
@@ -382,7 +61,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -401,13 +80,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -528,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -564,7 +236,6 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -599,6 +270,13 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -827,793 +505,640 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="2">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="2" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B2" s="4">
+        <v>2.012</v>
+      </c>
+      <c r="C2" s="5">
+        <v>0.875</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0.254</v>
+      </c>
+      <c r="E2" s="6">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="F2" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="H2" s="14">
+        <v>0.308</v>
+      </c>
+      <c r="I2" s="15">
+        <v>0.71699999999999997</v>
+      </c>
+      <c r="J2" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="K2" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="L2" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="M2" s="3">
+        <v>5.1999999999999998E-2</v>
+      </c>
     </row>
     <row r="3" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B3" s="7">
+        <v>2.0609999999999999</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.89200000000000002</v>
+      </c>
+      <c r="D3" s="8">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="E3" s="9">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="F3" s="3">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="G3" s="16">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="H3" s="17">
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="I3" s="18">
+        <v>0.68899999999999995</v>
+      </c>
+      <c r="J3" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="K3" s="3">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="L3" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="M3" s="3">
+        <v>5.1999999999999998E-2</v>
+      </c>
     </row>
     <row r="4" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="B4" s="7">
+        <v>1.992</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.9</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="F4" s="3">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="G4" s="16">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="H4" s="17">
+        <v>0.29599999999999999</v>
+      </c>
+      <c r="I4" s="18">
+        <v>0.60199999999999998</v>
+      </c>
+      <c r="J4" s="3">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="K4" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="L4" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="M4" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
     </row>
     <row r="5" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="B5" s="7">
+        <v>1.2749999999999999</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.157</v>
+      </c>
+      <c r="E5" s="9">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="G5" s="19">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="H5" s="20">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="I5" s="21">
+        <v>0.45900000000000002</v>
+      </c>
+      <c r="J5" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="K5" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="L5" s="3">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="M5" s="3">
+        <v>5.8000000000000003E-2</v>
+      </c>
     </row>
     <row r="6" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B6" s="7">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0.157</v>
+      </c>
+      <c r="E6" s="9">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="G6" s="19">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="H6" s="20">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="I6" s="21">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="J6" s="3">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="K6" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="L6" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="M6" s="3">
+        <v>5.3999999999999999E-2</v>
+      </c>
     </row>
     <row r="7" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="B7" s="10">
+        <v>1.2569999999999999</v>
+      </c>
+      <c r="C7" s="11">
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0.152</v>
+      </c>
+      <c r="E7" s="12">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="G7" s="22">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="H7" s="23">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="I7" s="24">
+        <v>0.45300000000000001</v>
+      </c>
+      <c r="J7" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="K7" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="L7" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="M7" s="3">
+        <v>5.3999999999999999E-2</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="B8" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="C8" s="3">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="D8" s="3">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="G8" s="3">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="H8" s="3">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="I8" s="3">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="J8" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="K8" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="L8" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="M8" s="3">
+        <v>5.2999999999999999E-2</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="13" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>115</v>
+        <v>8</v>
+      </c>
+      <c r="B9" s="3">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="C9" s="3">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="D9" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="E9" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="G9" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="H9" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="I9" s="3">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="J9" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="K9" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="L9" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="M9" s="3">
+        <v>5.2999999999999999E-2</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="2">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2">
-        <v>3</v>
-      </c>
-      <c r="E10" s="2">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2">
-        <v>5</v>
-      </c>
-      <c r="G10" s="2">
-        <v>6</v>
-      </c>
-      <c r="H10" s="2">
-        <v>7</v>
-      </c>
-      <c r="I10" s="2">
-        <v>8</v>
-      </c>
-      <c r="J10" s="2">
-        <v>9</v>
-      </c>
-      <c r="K10" s="2">
-        <v>10</v>
-      </c>
-      <c r="L10" s="2">
-        <v>11</v>
-      </c>
-      <c r="M10" s="2">
-        <v>12</v>
-      </c>
+      <c r="A10" s="25"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="26"/>
     </row>
     <row r="11" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="4">
-        <v>2.012</v>
-      </c>
-      <c r="C11" s="5">
-        <v>0.875</v>
-      </c>
-      <c r="D11" s="5">
-        <v>0.254</v>
-      </c>
-      <c r="E11" s="6">
-        <v>9.8000000000000004E-2</v>
-      </c>
-      <c r="F11" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="G11" s="14">
-        <v>0.13800000000000001</v>
-      </c>
-      <c r="H11" s="15">
-        <v>0.308</v>
-      </c>
-      <c r="I11" s="16">
-        <v>0.71699999999999997</v>
-      </c>
-      <c r="J11" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="K11" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="L11" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="M11" s="3">
-        <v>5.1999999999999998E-2</v>
-      </c>
+      <c r="A11" s="25"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
     </row>
     <row r="12" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7">
-        <v>2.0609999999999999</v>
-      </c>
-      <c r="C12" s="8">
-        <v>0.89200000000000002</v>
-      </c>
-      <c r="D12" s="8">
-        <v>0.25700000000000001</v>
-      </c>
-      <c r="E12" s="9">
-        <v>9.9000000000000005E-2</v>
-      </c>
-      <c r="F12" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="G12" s="17">
-        <v>0.13400000000000001</v>
-      </c>
-      <c r="H12" s="18">
-        <v>0.30199999999999999</v>
-      </c>
-      <c r="I12" s="19">
-        <v>0.68899999999999995</v>
-      </c>
-      <c r="J12" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="K12" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="L12" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="M12" s="3">
-        <v>5.1999999999999998E-2</v>
-      </c>
+      <c r="A12" s="25"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
     </row>
     <row r="13" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="7">
-        <v>1.992</v>
-      </c>
-      <c r="C13" s="8">
-        <v>0.9</v>
-      </c>
-      <c r="D13" s="8">
-        <v>0.25900000000000001</v>
-      </c>
-      <c r="E13" s="9">
-        <v>0.11700000000000001</v>
-      </c>
-      <c r="F13" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="G13" s="17">
-        <v>0.13400000000000001</v>
-      </c>
-      <c r="H13" s="18">
-        <v>0.29599999999999999</v>
-      </c>
-      <c r="I13" s="19">
-        <v>0.60199999999999998</v>
-      </c>
-      <c r="J13" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="K13" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="L13" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="M13" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
+      <c r="A13" s="25"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
     </row>
     <row r="14" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="7">
-        <v>1.2749999999999999</v>
-      </c>
-      <c r="C14" s="8">
-        <v>0.46100000000000002</v>
-      </c>
-      <c r="D14" s="8">
-        <v>0.157</v>
-      </c>
-      <c r="E14" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="F14" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="G14" s="20">
-        <v>8.5000000000000006E-2</v>
-      </c>
-      <c r="H14" s="21">
-        <v>0.28699999999999998</v>
-      </c>
-      <c r="I14" s="22">
-        <v>0.45900000000000002</v>
-      </c>
-      <c r="J14" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="K14" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="L14" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="M14" s="3">
-        <v>5.8000000000000003E-2</v>
-      </c>
+      <c r="A14" s="25"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
     </row>
     <row r="15" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="7">
-        <v>1.2569999999999999</v>
-      </c>
-      <c r="C15" s="8">
-        <v>0.46500000000000002</v>
-      </c>
-      <c r="D15" s="8">
-        <v>0.157</v>
-      </c>
-      <c r="E15" s="9">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="F15" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="G15" s="20">
-        <v>8.6999999999999994E-2</v>
-      </c>
-      <c r="H15" s="21">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="I15" s="22">
-        <v>0.44600000000000001</v>
-      </c>
-      <c r="J15" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="K15" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="L15" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="M15" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
+      <c r="A15" s="25"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
     </row>
     <row r="16" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="10">
-        <v>1.2569999999999999</v>
-      </c>
-      <c r="C16" s="11">
-        <v>0.46100000000000002</v>
-      </c>
-      <c r="D16" s="11">
-        <v>0.152</v>
-      </c>
-      <c r="E16" s="12">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="F16" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="G16" s="23">
-        <v>8.2000000000000003E-2</v>
-      </c>
-      <c r="H16" s="24">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="I16" s="25">
-        <v>0.45300000000000001</v>
-      </c>
-      <c r="J16" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="K16" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="L16" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="M16" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
+      <c r="A16" s="25"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
     </row>
     <row r="17" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="C17" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="D17" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="E17" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="F17" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="G17" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="H17" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="I17" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="J17" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="K17" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="L17" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="M17" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
+      <c r="A17" s="25"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="27"/>
     </row>
     <row r="18" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="C18" s="3">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="D18" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="E18" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="F18" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="G18" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="H18" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="I18" s="3">
-        <v>5.8999999999999997E-2</v>
-      </c>
-      <c r="J18" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="K18" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="L18" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="M18" s="3">
-        <v>5.2999999999999999E-2</v>
-      </c>
+      <c r="A18" s="25"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="27"/>
     </row>
     <row r="20" spans="1:13" ht="13" x14ac:dyDescent="0.15">
-      <c r="A20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="2">
-        <v>1</v>
-      </c>
-      <c r="C20" s="2">
-        <v>2</v>
-      </c>
-      <c r="D20" s="2">
-        <v>3</v>
-      </c>
-      <c r="E20" s="2">
-        <v>4</v>
-      </c>
-      <c r="F20" s="2">
-        <v>5</v>
-      </c>
-      <c r="G20" s="2">
-        <v>6</v>
-      </c>
-      <c r="H20" s="2">
-        <v>7</v>
-      </c>
-      <c r="I20" s="2">
-        <v>8</v>
-      </c>
-      <c r="J20" s="2">
-        <v>9</v>
-      </c>
-      <c r="K20" s="2">
-        <v>10</v>
-      </c>
-      <c r="L20" s="2">
-        <v>11</v>
-      </c>
-      <c r="M20" s="2">
-        <v>12</v>
-      </c>
+      <c r="A20" s="1"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
     </row>
     <row r="21" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
     </row>
     <row r="22" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
     </row>
     <row r="23" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
     </row>
     <row r="24" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>64</v>
-      </c>
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>76</v>
-      </c>
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
     </row>
     <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>88</v>
-      </c>
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
     </row>
     <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
     </row>
     <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>112</v>
-      </c>
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
     </row>
     <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
